--- a/public/assets/templates/grad-humanities-portfolio-checklist.xlsx
+++ b/public/assets/templates/grad-humanities-portfolio-checklist.xlsx
@@ -443,13 +443,13 @@
     <t>外語檢定之外，古文獻或研究語言的閱讀能力也算。誠實寫程度，這一欄在人文社科特別重要，空著比寫得謙虛更可惜。</t>
   </si>
   <si>
-    <t>搭配文章：人文社科研究所備審怎麼準備，自傳、學術 CV 與文字作品　https://tbd-web.vercel.app/pages/resources/humanities-graduate-cv.html?utm_source=tbd-web&amp;utm_medium=template&amp;utm_campaign=grad-humanities-portfolio-checklist</t>
+    <t>搭配文章：人文社科研究所備審怎麼準備，自傳、學術 CV 與文字作品　https://tbd-edu.com/pages/resources/humanities-graduate-cv.html?utm_source=tbd-web&amp;utm_medium=template&amp;utm_campaign=grad-humanities-portfolio-checklist</t>
   </si>
   <si>
     <t>上一階段是研究計畫書、下一階段是口試。備審的核心文件是計畫，其他文件都要往它對齊。</t>
   </si>
   <si>
-    <t>TBD Studio ｜ 研究所申請陪跑計畫　https://tbd-web.vercel.app/pages/resources/tools.html</t>
+    <t>TBD Studio ｜ 研究所申請陪跑計畫　https://tbd-edu.com/pages/resources/tools.html</t>
   </si>
   <si>
     <t>把候選作品全部列出來逐項評估，再決定送哪一到兩份。判準見「先讀這裡」分頁。</t>
